--- a/output/第10期計画_入力前段支援アプリの点検.xlsx
+++ b/output/第10期計画_入力前段支援アプリの点検.xlsx
@@ -1390,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>3,310,122,835</t>
+          <t>3,066,588,037</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>3,303,390,456</t>
+          <t>3,064,212,905</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>3,273,697,036</t>
+          <t>3,060,891,623</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>-0.20％</t>
+          <t>-0.08％</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>-1.10％</t>
+          <t>-0.19％</t>
         </is>
       </c>
     </row>
@@ -1602,183 +1602,288 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>3,310,122,835</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>3,303,390,456</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>3,273,697,036</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>-0.20％</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>-1.10％</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>3,408,932,536</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>3,401,493,779</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>3,362,233,819</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>-0.22％</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>-1.37％</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="17" t="inlineStr"/>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>3,258,825,048</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>3,253,593,714</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>3,226,818,202</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>-0.16％</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>-0.98％</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>3,240,335,214</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>3,234,564,583</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>3,217,793,100</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>-0.18％</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>-0.70％</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="17" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>第10期3か年計</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>9,031,900,444</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>9,027,348,708</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>9,020,228,881</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>-0.05％</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>-0.13％</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2　算定上の月額基準額（円）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>粒度</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>7区分との差</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="5" t="n">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>要介護度7区分（当方）</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>6,436.1</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>+0.0</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>要介護度ごとに利用率を固定する。年齢構成の変化による重度化が現れる</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="5" t="n">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>要介護・要支援の2区分（アプリ）</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>6,433.0</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>-3.1</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>要介護1〜5と要支援1〜2の別に受給率を固定する。重度化の大部分は拾えるが、要介護の中の構成の変化は拾えない</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="5" t="n">
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>区分なし（従前の一律）</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>6,428.2</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>-7.9</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>認定者数の総数の伸びを一律に乗じる。重度化は現れない</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>注1）第10期の3か年では、2区分と7区分の差は4,551,736円（0.05％）、月額で3円にとどまります。アプリの粒度でも第1次概算の水準は動きません。
 注2）中長期では差が開きます。令和22年度で2区分は-0.22％、一律は-1.37％です。改正法により令和22年度を含む中長期が記載事項となるため（確認事項No.114）、中長期では要介護度別が要ります。
@@ -1788,10 +1893,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_入力前段支援アプリの点検.xlsx
+++ b/output/第10期計画_入力前段支援アプリの点検.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>そのまま使える。当方が止まっているNo.123（施設・居住系の画面から進めない）・No.138（認定者数の編集項目の有無）は、この一覧のA02（最新操作手引）・A03（認証後画面の全キャプチャ）を受領すれば解ける。**発注者への資料提供依頼に転用する。**</t>
+          <t>そのまま使える。当方が止まっているNo.123（施設・居住系の画面から進めない）・No.138（認定者数の編集項目の有無）は、この一覧のA02（最新操作手引）・A03（認証後画面の全キャプチャ）を受領すれば解ける。発注者への資料提供依頼に転用する。</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
         <is>
           <t>注1）第10期の3か年では、2区分と7区分の差は4,551,736円（0.05％）、月額で3円にとどまります。アプリの粒度でも第1次概算の水準は動きません。
 注2）中長期では差が開きます。令和22年度で2区分は-0.22％、一律は-1.37％です。改正法により令和22年度を含む中長期が記載事項となるため（確認事項No.114）、中長期では要介護度別が要ります。
-注3）アプリは人口・認定の画面で年齢階級別×要介護度7区分の表を持っています。算定の側で7区分を2区分に束ねているだけであり、入力されたデータは7区分のまま残っています。**受給率の分母を要介護度別に取れば、当方と同じ粒度になります。**</t>
+注3）アプリは人口・認定の画面で年齢階級別×要介護度7区分の表を持っています。算定の側で7区分を2区分に束ねているだけであり、入力されたデータは7区分のまま残っています。受給率の分母を要介護度別に取れば、当方と同じ粒度になります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_入力前段支援アプリの点検.xlsx
+++ b/output/第10期計画_入力前段支援アプリの点検.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>6,436.1円</t>
+          <t>6,438.3円</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824円</t>
+          <t>2,088,171,801円</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824円</t>
+          <t>2,088,171,801円</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824円</t>
+          <t>2,088,171,801円</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>0.00円</t>
+          <t>-0.00円</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2,087,469,824円</t>
+          <t>2,088,171,801円</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">

--- a/output/第10期計画_入力前段支援アプリの点検.xlsx
+++ b/output/第10期計画_入力前段支援アプリの点検.xlsx
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する。月額で＋185〜＋374円に当たることを据え置き一覧に明示している。</t>
+          <t>単価を令和7年度で固定する。月額で＋245円〜＋327円に当たることを据え置き一覧に明示している。</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>注）1人1月あたり給付費の実績値の年度は、施設・居住系と在宅で別に選べます（当方が受領した出力の「施策反映の内容」から判明）。単価を令和7年度で固定するか令和8年度にするかは月額で＋185〜＋374円に当たり、第1次概算を止めている確認事項のうち効きが最も大きいものです。</t>
+          <t>注）1人1月あたり給付費の実績値の年度は、施設・居住系と在宅で別に選べます（当方が受領した出力の「施策反映の内容」から判明）。単価を令和7年度で固定するか令和8年度にするかは月額で＋245円〜＋327円に当たり、第1次概算を止めている確認事項のうち効きが最も大きいものです。</t>
         </is>
       </c>
     </row>
